--- a/data/trans_camb/IQ2606_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IQ2606_R2-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>15,88</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>1,53</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 29,17</t>
+          <t>-7,73; 19,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 17,11</t>
+          <t>-15,41; 24,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 19,09</t>
+          <t>2,6; 27,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 26,75</t>
+          <t>-32,17; 15,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 20,77</t>
+          <t>0,77; 20,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 19,18</t>
+          <t>-14,42; 14,98</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>24,3%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-7,37%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>-9,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 51,89</t>
+          <t>-10,63; 32,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 29,54</t>
+          <t>-22,43; 39,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 32,88</t>
+          <t>3,68; 48,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 46,13</t>
+          <t>-47,11; 24,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 34,17</t>
+          <t>1,07; 33,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 30,97</t>
+          <t>-21,55; 24,51</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,65</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>10,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,49</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>7,26</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 18,27</t>
+          <t>4,56; 20,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 19,55</t>
+          <t>-9,14; 19,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 21,06</t>
+          <t>2,44; 18,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 19,52</t>
+          <t>-11,39; 17,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 16,7</t>
+          <t>5,43; 16,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 17,05</t>
+          <t>-4,32; 16,07</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>12,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 25,02</t>
+          <t>5,88; 29,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 25,65</t>
+          <t>-10,81; 26,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 29,35</t>
+          <t>2,97; 25,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 26,36</t>
+          <t>-13,81; 23,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 22,32</t>
+          <t>6,5; 22,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 22,38</t>
+          <t>-5,24; 20,84</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-22,81</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16,7</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,53</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>15,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,82</t>
+          <t>19,6</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,27; -8,92</t>
+          <t>-17,67; 9,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 30,4</t>
+          <t>2,32; 40,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 10,46</t>
+          <t>-37,06; -8,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 42,66</t>
+          <t>-4,04; 31,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -3,85</t>
+          <t>-22,53; -2,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 33,2</t>
+          <t>2,97; 31,15</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-9,22%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-35,31%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,22%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,2; -15,0</t>
+          <t>-32,36; 21,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 51,32</t>
+          <t>5,22; 95,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 24,75</t>
+          <t>-52,77; -13,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 97,22</t>
+          <t>-5,55; 52,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -7,84</t>
+          <t>-37,21; -6,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 62,52</t>
+          <t>5,07; 58,74</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33,67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>53,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>29,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>29,87</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33,67</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53,64</t>
+          <t>30,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,73</t>
+          <t>39,51</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,07; 42,48</t>
+          <t>22,22; 45,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 51,12</t>
+          <t>43,2; 62,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,71; 45,25</t>
+          <t>16,26; 41,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,17; 62,31</t>
+          <t>2,2; 50,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,54; 40,5</t>
+          <t>22,24; 40,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,78; 53,13</t>
+          <t>17,71; 51,49</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>72,63%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>115,7%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>66,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>68,04%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>72,63%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115,7%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,95; 119,13</t>
+          <t>42,04; 122,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,58; 134,56</t>
+          <t>76,05; 164,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,1; 117,79</t>
+          <t>31,16; 115,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79,12; 165,35</t>
+          <t>7,69; 134,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,25; 102,3</t>
+          <t>43,6; 105,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,06; 129,98</t>
+          <t>39,14; 126,69</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32,99</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>4,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>17,55</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33,66</t>
+          <t>18,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,77</t>
+          <t>25,69</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 21,77</t>
+          <t>-18,89; 16,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 36,87</t>
+          <t>12,07; 49,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 16,12</t>
+          <t>-12,46; 20,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,01; 49,28</t>
+          <t>-4,89; 35,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 13,98</t>
+          <t>-10,24; 14,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,95; 37,99</t>
+          <t>11,12; 38,86</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-0,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>58,84%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-0,44%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 39,49</t>
+          <t>-29,15; 33,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 71,14</t>
+          <t>21,15; 108,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 33,69</t>
+          <t>-17,27; 40,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,76; 112,1</t>
+          <t>-5,36; 64,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 26,06</t>
+          <t>-15,8; 28,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,25; 73,04</t>
+          <t>17,81; 73,69</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>34,81</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>23,61</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>29,63</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>29,28</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>34,81</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23,88</t>
+          <t>28,04</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,47</t>
+          <t>25,07</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>14,62; 43,71</t>
+          <t>20,78; 47,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 48,57</t>
+          <t>1,46; 42,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20,48; 47,86</t>
+          <t>14,72; 42,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 41,83</t>
+          <t>0,02; 47,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,43; 42,57</t>
+          <t>21,82; 42,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,94; 39,14</t>
+          <t>8,03; 39,27</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>69,57%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>47,18%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>57,96%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>57,26%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24,61; 111,27</t>
+          <t>35,55; 124,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,47; 115,54</t>
+          <t>3,44; 101,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36,14; 122,38</t>
+          <t>24,91; 104,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,48; 97,18</t>
+          <t>2,81; 108,15</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>39,96; 99,08</t>
+          <t>39,45; 98,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,14; 87,53</t>
+          <t>15,69; 88,2</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>19,9</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>41,43</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>17,1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>37,21</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>19,9</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41,22</t>
+          <t>34,92</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,98</t>
+          <t>38,21</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,72; 26,55</t>
+          <t>9,96; 28,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>25,56; 47,18</t>
+          <t>28,71; 50,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10,33; 29,42</t>
+          <t>7,93; 26,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27,3; 51,93</t>
+          <t>21,3; 45,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,55; 24,89</t>
+          <t>11,88; 24,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,11; 46,12</t>
+          <t>28,93; 45,75</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>31,35%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>68,23%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,16; 54,11</t>
+          <t>18,67; 68,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>44,39; 99,33</t>
+          <t>55,68; 117,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,48; 68,29</t>
+          <t>13,62; 55,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52,22; 124,59</t>
+          <t>37,52; 92,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,37; 52,43</t>
+          <t>21,47; 52,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,74; 97,99</t>
+          <t>54,55; 96,82</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>15,46</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>31,06</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>4,82</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>25,38</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>15,46</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30,71</t>
+          <t>25,79</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,03</t>
+          <t>28,41</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 12,42</t>
+          <t>7,29; 23,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,99; 33,79</t>
+          <t>18,7; 39,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7,34; 23,84</t>
+          <t>-3,0; 12,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19,43; 38,95</t>
+          <t>12,84; 33,31</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,13; 15,57</t>
+          <t>4,29; 16,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,81; 34,16</t>
+          <t>19,86; 34,36</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>25,51%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>51,24%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>7,22%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 20,56</t>
+          <t>11,35; 40,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>19,39; 53,53</t>
+          <t>29,72; 70,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11,18; 43,26</t>
+          <t>-4,23; 20,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31,34; 68,83</t>
+          <t>19,55; 54,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,39; 26,15</t>
+          <t>6,62; 26,69</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,42; 56,43</t>
+          <t>30,35; 57,65</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>15,81</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>28,1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>10,93</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>21,57</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>15,81</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28,13</t>
+          <t>20,62</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>24,6</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,09</t>
+          <t>12,05; 19,9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>15,17; 26,66</t>
+          <t>22,41; 32,89</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,89; 19,98</t>
+          <t>6,59; 14,91</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22,44; 33,34</t>
+          <t>14,03; 26,44</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,29</t>
+          <t>10,45; 16,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,1; 28,76</t>
+          <t>20,05; 28,52</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>48,81%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>17,6%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>10,32; 25,11</t>
+          <t>20,05; 36,22</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>24,02; 44,05</t>
+          <t>38,09; 59,55</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>19,88; 36,92</t>
+          <t>10,25; 25,34</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>38,02; 59,66</t>
+          <t>22,51; 44,71</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>17,15; 27,92</t>
+          <t>16,96; 27,98</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,36</t>
+          <t>32,91; 48,94</t>
         </is>
       </c>
     </row>
